--- a/results/Int Task Remove ACC -0.5/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_3_permute.xlsx
@@ -440,527 +440,527 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6309338068429858</v>
+        <v>0.6448720196540105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6375409843047593</v>
+        <v>0.6452233897489372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6410475868682703</v>
+        <v>0.6457513321895467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6494027418224821</v>
+        <v>0.6451898498762396</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6595871507860398</v>
+        <v>0.6455059055020298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6594865311679471</v>
+        <v>0.6467259405538587</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6527469688118226</v>
+        <v>0.6438090363870352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6598361266664348</v>
+        <v>0.6448966865445129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.660710115412654</v>
+        <v>0.6481949514860825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6732552700190451</v>
+        <v>0.6457371354180346</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6742034368964154</v>
+        <v>0.6382912836791785</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6558333469385726</v>
+        <v>0.6421192656577968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6920455844136485</v>
+        <v>0.6408197286854996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6888514882830495</v>
+        <v>0.6424000068144504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7163147878540941</v>
+        <v>0.6448613720753764</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7138851878694266</v>
+        <v>0.6503049466520818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7077017840372921</v>
+        <v>0.6500595199645649</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7064375615341315</v>
+        <v>0.6251317637855975</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7093773579950183</v>
+        <v>0.6520919652661789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6987356355291243</v>
+        <v>0.6532202536821101</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6984195799033341</v>
+        <v>0.6421071984020114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6984195799033341</v>
+        <v>0.6423879395586649</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7194222836784687</v>
+        <v>0.6295091608217376</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7252614158014326</v>
+        <v>0.6522827343833739</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7058760792208244</v>
+        <v>0.6238607978159687</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7017355908092942</v>
+        <v>0.6123610579718066</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.683344383153827</v>
+        <v>0.6096684627948759</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6626965986664972</v>
+        <v>0.6098432605441197</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6616795774472928</v>
+        <v>0.6204796592206967</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.679659433648194</v>
+        <v>0.6204796592206967</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6788896137129455</v>
+        <v>0.6483896247154435</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7093351225997695</v>
+        <v>0.6444645723116107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7093351225997695</v>
+        <v>0.6444645723116107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7163854167923672</v>
+        <v>0.626292349856719</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7168409556982647</v>
+        <v>0.6486370034590434</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7332405337702153</v>
+        <v>0.6386980211830027</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7332405337702153</v>
+        <v>0.6082471885068617</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7115510611731786</v>
+        <v>0.6023922624755904</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.700701178544987</v>
+        <v>0.5918582580135452</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7008053473559578</v>
+        <v>0.5941694924157297</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6997512370711776</v>
+        <v>0.6031832001084634</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6830568985307052</v>
+        <v>0.6035345702033901</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6834506814805246</v>
+        <v>0.5771273329732086</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6464317124642684</v>
+        <v>0.6074315839834863</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6790207563897894</v>
+        <v>0.5983101582869039</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6518046581027008</v>
+        <v>0.6062044505459013</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6495567767933894</v>
+        <v>0.5888762261574095</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6390563122040417</v>
+        <v>0.5887032030046048</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5895065628125508</v>
+        <v>0.593269239642213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.624013058190437</v>
+        <v>0.5924270161722522</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.623836485844754</v>
+        <v>0.5453627665532581</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4960572016317769</v>
+        <v>0.5746675648490777</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4947629884487968</v>
+        <v>0.5283379981558394</v>
       </c>
     </row>
     <row r="55">
@@ -970,277 +970,277 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4954621794457722</v>
+        <v>0.5255657235987964</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4856926711296584</v>
+        <v>0.5211356210484174</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4856926711296584</v>
+        <v>0.5226064065770804</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4886095752964819</v>
+        <v>0.5397069502424454</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4856538074676438</v>
+        <v>0.5440646492581122</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4954197665908796</v>
+        <v>0.4553999549962343</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4954197665908796</v>
+        <v>0.43220083320852</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4949642276849822</v>
+        <v>0.4308995216397839</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4934934421563192</v>
+        <v>0.4308995216397839</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.491145118688559</v>
+        <v>0.4320489277533396</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4889327293080281</v>
+        <v>0.4286040811459066</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4898102672471253</v>
+        <v>0.4384935521812984</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4855585116388682</v>
+        <v>0.4384935521812984</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4878768444268089</v>
+        <v>0.4338622103947341</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.503254077490238</v>
+        <v>0.4277583084830679</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5035012787741939</v>
+        <v>0.4179958985527101</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5006285620587022</v>
+        <v>0.4382607251284986</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4995038228356489</v>
+        <v>0.4280869637435751</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.500734505466112</v>
+        <v>0.4426959740085507</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4839817827027956</v>
+        <v>0.499961846176561</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4931844849162852</v>
+        <v>0.5152366850254584</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4954639540422113</v>
+        <v>0.4743721655258378</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5001041688109708</v>
+        <v>0.5118280401853814</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5001394832801073</v>
+        <v>0.496182488140372</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5010876501574777</v>
+        <v>0.4965338582352987</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5008069090008241</v>
+        <v>0.4858197322346925</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5015078745942385</v>
+        <v>0.4974289646791423</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5016138180016482</v>
+        <v>0.4842147872152394</v>
       </c>
     </row>
     <row r="83">
@@ -1250,77 +1250,77 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5016138180016482</v>
+        <v>0.4842147872152394</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5016138180016482</v>
+        <v>0.5034200022572867</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5013330768449946</v>
+        <v>0.4943903231966019</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5046295671901253</v>
+        <v>0.4953438138632894</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5046295671901253</v>
+        <v>0.4968887775231035</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.499998225403561</v>
+        <v>0.4968887775231035</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4998940565925903</v>
+        <v>0.4976956865239276</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4995780009668002</v>
+        <v>0.4998409961590635</v>
       </c>
     </row>
   </sheetData>
